--- a/review-results/河北实时运行及市场出清数据-20261015.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20261015.xlsx
@@ -4289,9 +4289,7 @@
       <ns0:c r="C2" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D2" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D2" s="1"/>
       <ns0:c r="E2" s="1" t="n">
         <ns0:v>389.39</ns0:v>
       </ns0:c>
@@ -4328,9 +4326,7 @@
       <ns0:c r="P2" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q2" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q2"/>
     </ns0:row>
     <ns0:row r="3" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A3" s="6" t="n">
@@ -4342,9 +4338,7 @@
       <ns0:c r="C3" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D3" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D3" s="1"/>
       <ns0:c r="E3" s="1" t="n">
         <ns0:v>390.61</ns0:v>
       </ns0:c>
@@ -4381,9 +4375,7 @@
       <ns0:c r="P3" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q3" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q3"/>
     </ns0:row>
     <ns0:row r="4" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A4" s="6" t="n">
@@ -4395,9 +4387,7 @@
       <ns0:c r="C4" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D4" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D4" s="1"/>
       <ns0:c r="E4" s="1" t="n">
         <ns0:v>394.48</ns0:v>
       </ns0:c>
@@ -4434,9 +4424,7 @@
       <ns0:c r="P4" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q4" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q4"/>
     </ns0:row>
     <ns0:row r="5" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A5" s="6" t="n">
@@ -4448,9 +4436,7 @@
       <ns0:c r="C5" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D5" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D5" s="1"/>
       <ns0:c r="E5" s="1" t="n">
         <ns0:v>390.04</ns0:v>
       </ns0:c>
@@ -4487,9 +4473,7 @@
       <ns0:c r="P5" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q5" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q5"/>
     </ns0:row>
     <ns0:row r="6" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A6" s="6" t="n">
@@ -4501,9 +4485,7 @@
       <ns0:c r="C6" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D6" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D6" s="1"/>
       <ns0:c r="E6" s="1" t="n">
         <ns0:v>390.61</ns0:v>
       </ns0:c>
@@ -4540,9 +4522,7 @@
       <ns0:c r="P6" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q6" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q6"/>
     </ns0:row>
     <ns0:row r="7" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A7" s="6" t="n">
@@ -4554,9 +4534,7 @@
       <ns0:c r="C7" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D7" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D7" s="1"/>
       <ns0:c r="E7" s="1" t="n">
         <ns0:v>390.61</ns0:v>
       </ns0:c>
@@ -4593,9 +4571,7 @@
       <ns0:c r="P7" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q7" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q7"/>
     </ns0:row>
     <ns0:row r="8" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A8" s="6" t="n">
@@ -4607,9 +4583,7 @@
       <ns0:c r="C8" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D8" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D8" s="1"/>
       <ns0:c r="E8" s="1" t="n">
         <ns0:v>338.23</ns0:v>
       </ns0:c>
@@ -4646,9 +4620,7 @@
       <ns0:c r="P8" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q8" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q8"/>
     </ns0:row>
     <ns0:row r="9" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A9" s="6" t="n">
@@ -4660,9 +4632,7 @@
       <ns0:c r="C9" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D9" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D9" s="1"/>
       <ns0:c r="E9" s="1" t="n">
         <ns0:v>334.67</ns0:v>
       </ns0:c>
@@ -4699,9 +4669,7 @@
       <ns0:c r="P9" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q9" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q9"/>
     </ns0:row>
     <ns0:row r="10" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A10" s="6" t="n">
@@ -4713,9 +4681,7 @@
       <ns0:c r="C10" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D10" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D10" s="1"/>
       <ns0:c r="E10" s="1" t="n">
         <ns0:v>475.19</ns0:v>
       </ns0:c>
@@ -4752,9 +4718,7 @@
       <ns0:c r="P10" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q10" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q10"/>
     </ns0:row>
     <ns0:row r="11" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A11" s="6" t="n">
@@ -4766,9 +4730,7 @@
       <ns0:c r="C11" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D11" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D11" s="1"/>
       <ns0:c r="E11" s="1" t="n">
         <ns0:v>400.57</ns0:v>
       </ns0:c>
@@ -4805,9 +4767,7 @@
       <ns0:c r="P11" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q11" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q11"/>
     </ns0:row>
     <ns0:row r="12" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A12" s="6" t="n">
@@ -4819,9 +4779,7 @@
       <ns0:c r="C12" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D12" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D12" s="1"/>
       <ns0:c r="E12" s="1" t="n">
         <ns0:v>391.04</ns0:v>
       </ns0:c>
@@ -4858,9 +4816,7 @@
       <ns0:c r="P12" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q12" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q12"/>
     </ns0:row>
     <ns0:row r="13" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A13" s="6" t="n">
@@ -4872,9 +4828,7 @@
       <ns0:c r="C13" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D13" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D13" s="1"/>
       <ns0:c r="E13" s="1" t="n">
         <ns0:v>394.48</ns0:v>
       </ns0:c>
@@ -4911,9 +4865,7 @@
       <ns0:c r="P13" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q13" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q13"/>
     </ns0:row>
     <ns0:row r="14" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A14" s="6" t="n">
@@ -4925,9 +4877,7 @@
       <ns0:c r="C14" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D14" s="1" t="n">
-        <ns0:v>389</ns0:v>
-      </ns0:c>
+      <ns0:c r="D14" s="1"/>
       <ns0:c r="E14" s="1" t="n">
         <ns0:v>423.26</ns0:v>
       </ns0:c>
@@ -4964,9 +4914,7 @@
       <ns0:c r="P14" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q14" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q14"/>
     </ns0:row>
     <ns0:row r="15" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A15" s="6" t="n">
@@ -4978,9 +4926,7 @@
       <ns0:c r="C15" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D15" s="1" t="n">
-        <ns0:v>389</ns0:v>
-      </ns0:c>
+      <ns0:c r="D15" s="1"/>
       <ns0:c r="E15" s="1" t="n">
         <ns0:v>425.14</ns0:v>
       </ns0:c>
@@ -5017,9 +4963,7 @@
       <ns0:c r="P15" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q15" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q15"/>
     </ns0:row>
     <ns0:row r="16" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A16" s="6" t="n">
@@ -5031,9 +4975,7 @@
       <ns0:c r="C16" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D16" s="1" t="n">
-        <ns0:v>389</ns0:v>
-      </ns0:c>
+      <ns0:c r="D16" s="1"/>
       <ns0:c r="E16" s="1" t="n">
         <ns0:v>469.48</ns0:v>
       </ns0:c>
@@ -5070,9 +5012,7 @@
       <ns0:c r="P16" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q16" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q16"/>
     </ns0:row>
     <ns0:row r="17" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A17" s="6" t="n">
@@ -5084,9 +5024,7 @@
       <ns0:c r="C17" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D17" s="1" t="n">
-        <ns0:v>389</ns0:v>
-      </ns0:c>
+      <ns0:c r="D17" s="1"/>
       <ns0:c r="E17" s="1" t="n">
         <ns0:v>445</ns0:v>
       </ns0:c>
@@ -5123,9 +5061,7 @@
       <ns0:c r="P17" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q17" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q17"/>
     </ns0:row>
     <ns0:row r="18" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A18" s="6" t="n">
@@ -5137,9 +5073,7 @@
       <ns0:c r="C18" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D18" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D18" s="1"/>
       <ns0:c r="E18" s="1" t="n">
         <ns0:v>470.5</ns0:v>
       </ns0:c>
@@ -5176,9 +5110,7 @@
       <ns0:c r="P18" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q18" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q18"/>
     </ns0:row>
     <ns0:row r="19" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A19" s="6" t="n">
@@ -5190,9 +5122,7 @@
       <ns0:c r="C19" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D19" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D19" s="1"/>
       <ns0:c r="E19" s="1" t="n">
         <ns0:v>469.1</ns0:v>
       </ns0:c>
@@ -5229,9 +5159,7 @@
       <ns0:c r="P19" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q19" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q19"/>
     </ns0:row>
     <ns0:row r="20" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A20" s="6" t="n">
@@ -5243,9 +5171,7 @@
       <ns0:c r="C20" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D20" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D20" s="1"/>
       <ns0:c r="E20" s="1" t="n">
         <ns0:v>469.1</ns0:v>
       </ns0:c>
@@ -5282,9 +5208,7 @@
       <ns0:c r="P20" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q20" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q20"/>
     </ns0:row>
     <ns0:row r="21" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A21" s="6" t="n">
@@ -5296,9 +5220,7 @@
       <ns0:c r="C21" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D21" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D21" s="1"/>
       <ns0:c r="E21" s="1" t="n">
         <ns0:v>435.26</ns0:v>
       </ns0:c>
@@ -5335,9 +5257,7 @@
       <ns0:c r="P21" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q21" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q21"/>
     </ns0:row>
     <ns0:row r="22" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A22" s="6" t="n">
@@ -5349,9 +5269,7 @@
       <ns0:c r="C22" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D22" s="1" t="n">
-        <ns0:v>398.79</ns0:v>
-      </ns0:c>
+      <ns0:c r="D22" s="1"/>
       <ns0:c r="E22" s="1" t="n">
         <ns0:v>433.17</ns0:v>
       </ns0:c>
@@ -5388,9 +5306,7 @@
       <ns0:c r="P22" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q22" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q22"/>
     </ns0:row>
     <ns0:row r="23" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A23" s="6" t="n">
@@ -5402,9 +5318,7 @@
       <ns0:c r="C23" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D23" s="1" t="n">
-        <ns0:v>398.79</ns0:v>
-      </ns0:c>
+      <ns0:c r="D23" s="1"/>
       <ns0:c r="E23" s="1" t="n">
         <ns0:v>465.52</ns0:v>
       </ns0:c>
@@ -5441,9 +5355,7 @@
       <ns0:c r="P23" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q23" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q23"/>
     </ns0:row>
     <ns0:row r="24" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A24" s="6" t="n">
@@ -5455,9 +5367,7 @@
       <ns0:c r="C24" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D24" s="1" t="n">
-        <ns0:v>398.79</ns0:v>
-      </ns0:c>
+      <ns0:c r="D24" s="1"/>
       <ns0:c r="E24" s="1" t="n">
         <ns0:v>432.58</ns0:v>
       </ns0:c>
@@ -5494,9 +5404,7 @@
       <ns0:c r="P24" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q24" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q24"/>
     </ns0:row>
     <ns0:row r="25" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A25" s="6" t="n">
@@ -5508,9 +5416,7 @@
       <ns0:c r="C25" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D25" s="1" t="n">
-        <ns0:v>398.79</ns0:v>
-      </ns0:c>
+      <ns0:c r="D25" s="1"/>
       <ns0:c r="E25" s="1" t="n">
         <ns0:v>473.23</ns0:v>
       </ns0:c>
@@ -5547,9 +5453,7 @@
       <ns0:c r="P25" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q25" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q25"/>
     </ns0:row>
     <ns0:row r="26" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A26" s="6" t="n">
@@ -5561,9 +5465,7 @@
       <ns0:c r="C26" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D26" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D26" s="1"/>
       <ns0:c r="E26" s="1" t="n">
         <ns0:v>475.2</ns0:v>
       </ns0:c>
@@ -5600,9 +5502,7 @@
       <ns0:c r="P26" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q26" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q26"/>
     </ns0:row>
     <ns0:row r="27" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A27" s="6" t="n">
@@ -5614,9 +5514,7 @@
       <ns0:c r="C27" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D27" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D27" s="1"/>
       <ns0:c r="E27" s="1" t="n">
         <ns0:v>425.45</ns0:v>
       </ns0:c>
@@ -5653,9 +5551,7 @@
       <ns0:c r="P27" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q27" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q27"/>
     </ns0:row>
     <ns0:row r="28" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A28" s="6" t="n">
@@ -5667,9 +5563,7 @@
       <ns0:c r="C28" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D28" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D28" s="1"/>
       <ns0:c r="E28" s="1" t="n">
         <ns0:v>424.07</ns0:v>
       </ns0:c>
@@ -5706,9 +5600,7 @@
       <ns0:c r="P28" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q28" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q28"/>
     </ns0:row>
     <ns0:row r="29" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A29" s="6" t="n">
@@ -5720,9 +5612,7 @@
       <ns0:c r="C29" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D29" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D29" s="1"/>
       <ns0:c r="E29" s="1" t="n">
         <ns0:v>433.17</ns0:v>
       </ns0:c>
@@ -5759,9 +5649,7 @@
       <ns0:c r="P29" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q29" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q29"/>
     </ns0:row>
     <ns0:row r="30" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A30" s="6" t="n">
@@ -5773,9 +5661,7 @@
       <ns0:c r="C30" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D30" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D30" s="1"/>
       <ns0:c r="E30" s="1" t="n">
         <ns0:v>475.19</ns0:v>
       </ns0:c>
@@ -5812,9 +5698,7 @@
       <ns0:c r="P30" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q30" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q30"/>
     </ns0:row>
     <ns0:row r="31" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A31" s="6" t="n">
@@ -5826,9 +5710,7 @@
       <ns0:c r="C31" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D31" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D31" s="1"/>
       <ns0:c r="E31" s="1" t="n">
         <ns0:v>465.52</ns0:v>
       </ns0:c>
@@ -5865,9 +5747,7 @@
       <ns0:c r="P31" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q31" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q31"/>
     </ns0:row>
     <ns0:row r="32" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A32" s="6" t="n">
@@ -5879,9 +5759,7 @@
       <ns0:c r="C32" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D32" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D32" s="1"/>
       <ns0:c r="E32" s="1" t="n">
         <ns0:v>425.45</ns0:v>
       </ns0:c>
@@ -5918,9 +5796,7 @@
       <ns0:c r="P32" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q32" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q32"/>
     </ns0:row>
     <ns0:row r="33" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A33" s="6" t="n">
@@ -5932,9 +5808,7 @@
       <ns0:c r="C33" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D33" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D33" s="1"/>
       <ns0:c r="E33" s="1" t="n">
         <ns0:v>343.05</ns0:v>
       </ns0:c>
@@ -5971,9 +5845,7 @@
       <ns0:c r="P33" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q33" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q33"/>
     </ns0:row>
     <ns0:row r="34" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A34" s="6" t="n">
@@ -5985,9 +5857,7 @@
       <ns0:c r="C34" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D34" s="1" t="n">
-        <ns0:v>193</ns0:v>
-      </ns0:c>
+      <ns0:c r="D34" s="1"/>
       <ns0:c r="E34" s="1" t="n">
         <ns0:v>343.05</ns0:v>
       </ns0:c>
@@ -6024,9 +5894,7 @@
       <ns0:c r="P34" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q34" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q34"/>
     </ns0:row>
     <ns0:row r="35" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A35" s="6" t="n">
@@ -6038,9 +5906,7 @@
       <ns0:c r="C35" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D35" s="1" t="n">
-        <ns0:v>193</ns0:v>
-      </ns0:c>
+      <ns0:c r="D35" s="1"/>
       <ns0:c r="E35" s="1" t="n">
         <ns0:v>334.41</ns0:v>
       </ns0:c>
@@ -6077,9 +5943,7 @@
       <ns0:c r="P35" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q35" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q35"/>
     </ns0:row>
     <ns0:row r="36" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A36" s="6" t="n">
@@ -6091,9 +5955,7 @@
       <ns0:c r="C36" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D36" s="1" t="n">
-        <ns0:v>193</ns0:v>
-      </ns0:c>
+      <ns0:c r="D36" s="1"/>
       <ns0:c r="E36" s="1" t="n">
         <ns0:v>276.08</ns0:v>
       </ns0:c>
@@ -6130,9 +5992,7 @@
       <ns0:c r="P36" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q36" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q36"/>
     </ns0:row>
     <ns0:row r="37" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A37" s="6" t="n">
@@ -6144,9 +6004,7 @@
       <ns0:c r="C37" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D37" s="1" t="n">
-        <ns0:v>193</ns0:v>
-      </ns0:c>
+      <ns0:c r="D37" s="1"/>
       <ns0:c r="E37" s="1" t="n">
         <ns0:v>235.41</ns0:v>
       </ns0:c>
@@ -6183,9 +6041,7 @@
       <ns0:c r="P37" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q37" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q37"/>
     </ns0:row>
     <ns0:row r="38" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A38" s="6" t="n">
@@ -6197,9 +6053,7 @@
       <ns0:c r="C38" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D38" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D38" s="1"/>
       <ns0:c r="E38" s="1" t="n">
         <ns0:v>199.14</ns0:v>
       </ns0:c>
@@ -6236,9 +6090,7 @@
       <ns0:c r="P38" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q38" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q38"/>
     </ns0:row>
     <ns0:row r="39" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A39" s="6" t="n">
@@ -6250,9 +6102,7 @@
       <ns0:c r="C39" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D39" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D39" s="1"/>
       <ns0:c r="E39" s="1" t="n">
         <ns0:v>280</ns0:v>
       </ns0:c>
@@ -6289,9 +6139,7 @@
       <ns0:c r="P39" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q39" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q39"/>
     </ns0:row>
     <ns0:row r="40" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A40" s="6" t="n">
@@ -6303,9 +6151,7 @@
       <ns0:c r="C40" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D40" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D40" s="1"/>
       <ns0:c r="E40" s="1" t="n">
         <ns0:v>330.54</ns0:v>
       </ns0:c>
@@ -6342,9 +6188,7 @@
       <ns0:c r="P40" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q40" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q40"/>
     </ns0:row>
     <ns0:row r="41" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A41" s="6" t="n">
@@ -6356,9 +6200,7 @@
       <ns0:c r="C41" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D41" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D41" s="1"/>
       <ns0:c r="E41" s="1" t="n">
         <ns0:v>278.94</ns0:v>
       </ns0:c>
@@ -6395,9 +6237,7 @@
       <ns0:c r="P41" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q41" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q41"/>
     </ns0:row>
     <ns0:row r="42" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A42" s="6" t="n">
@@ -6409,9 +6249,7 @@
       <ns0:c r="C42" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D42" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D42" s="1"/>
       <ns0:c r="E42" s="1" t="n">
         <ns0:v>335.98</ns0:v>
       </ns0:c>
@@ -6448,9 +6286,7 @@
       <ns0:c r="P42" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q42" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q42"/>
     </ns0:row>
     <ns0:row r="43" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A43" s="6" t="n">
@@ -6462,9 +6298,7 @@
       <ns0:c r="C43" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D43" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D43" s="1"/>
       <ns0:c r="E43" s="1" t="n">
         <ns0:v>330.01</ns0:v>
       </ns0:c>
@@ -6501,9 +6335,7 @@
       <ns0:c r="P43" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q43" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q43"/>
     </ns0:row>
     <ns0:row r="44" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A44" s="6" t="n">
@@ -6515,9 +6347,7 @@
       <ns0:c r="C44" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D44" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D44" s="1"/>
       <ns0:c r="E44" s="1" t="n">
         <ns0:v>334.67</ns0:v>
       </ns0:c>
@@ -6554,9 +6384,7 @@
       <ns0:c r="P44" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q44" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q44"/>
     </ns0:row>
     <ns0:row r="45" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A45" s="6" t="n">
@@ -6568,9 +6396,7 @@
       <ns0:c r="C45" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D45" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D45" s="1"/>
       <ns0:c r="E45" s="1" t="n">
         <ns0:v>335.98</ns0:v>
       </ns0:c>
@@ -6607,9 +6433,7 @@
       <ns0:c r="P45" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q45" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q45"/>
     </ns0:row>
     <ns0:row r="46" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A46" s="6" t="n">
@@ -6621,9 +6445,7 @@
       <ns0:c r="C46" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D46" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D46" s="1"/>
       <ns0:c r="E46" s="1" t="n">
         <ns0:v>203.89</ns0:v>
       </ns0:c>
@@ -6660,9 +6482,7 @@
       <ns0:c r="P46" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q46" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q46"/>
     </ns0:row>
     <ns0:row r="47" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A47" s="6" t="n">
@@ -6674,9 +6494,7 @@
       <ns0:c r="C47" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D47" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D47" s="1"/>
       <ns0:c r="E47" s="1" t="n">
         <ns0:v>330.79</ns0:v>
       </ns0:c>
@@ -6713,9 +6531,7 @@
       <ns0:c r="P47" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q47" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q47"/>
     </ns0:row>
     <ns0:row r="48" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A48" s="6" t="n">
@@ -6727,9 +6543,7 @@
       <ns0:c r="C48" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D48" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D48" s="1"/>
       <ns0:c r="E48" s="1" t="n">
         <ns0:v>280.95</ns0:v>
       </ns0:c>
@@ -6766,9 +6580,7 @@
       <ns0:c r="P48" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q48" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q48"/>
     </ns0:row>
     <ns0:row r="49" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A49" s="6" t="n">
@@ -6780,9 +6592,7 @@
       <ns0:c r="C49" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D49" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D49" s="1"/>
       <ns0:c r="E49" s="1" t="n">
         <ns0:v>206.83</ns0:v>
       </ns0:c>
@@ -6819,9 +6629,7 @@
       <ns0:c r="P49" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q49" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q49"/>
     </ns0:row>
     <ns0:row r="50" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A50" s="6" t="n">
@@ -6833,9 +6641,7 @@
       <ns0:c r="C50" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D50" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D50" s="1"/>
       <ns0:c r="E50" s="1" t="n">
         <ns0:v>328.38</ns0:v>
       </ns0:c>
@@ -6872,9 +6678,7 @@
       <ns0:c r="P50" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q50" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q50"/>
     </ns0:row>
     <ns0:row r="51" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A51" s="6" t="n">
@@ -6886,9 +6690,7 @@
       <ns0:c r="C51" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D51" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D51" s="1"/>
       <ns0:c r="E51" s="1" t="n">
         <ns0:v>226.8</ns0:v>
       </ns0:c>
@@ -6925,9 +6727,7 @@
       <ns0:c r="P51" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q51" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q51"/>
     </ns0:row>
     <ns0:row r="52" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A52" s="6" t="n">
@@ -6939,9 +6739,7 @@
       <ns0:c r="C52" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D52" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D52" s="1"/>
       <ns0:c r="E52" s="1" t="n">
         <ns0:v>231.86</ns0:v>
       </ns0:c>
@@ -6978,9 +6776,7 @@
       <ns0:c r="P52" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q52" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q52"/>
     </ns0:row>
     <ns0:row r="53" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A53" s="6" t="n">
@@ -6992,9 +6788,7 @@
       <ns0:c r="C53" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D53" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D53" s="1"/>
       <ns0:c r="E53" s="1" t="n">
         <ns0:v>330.79</ns0:v>
       </ns0:c>
@@ -7031,9 +6825,7 @@
       <ns0:c r="P53" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q53" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q53"/>
     </ns0:row>
     <ns0:row r="54" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A54" s="6" t="n">
@@ -7045,9 +6837,7 @@
       <ns0:c r="C54" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D54" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D54" s="1"/>
       <ns0:c r="E54" s="1" t="n">
         <ns0:v>237</ns0:v>
       </ns0:c>
@@ -7084,9 +6874,7 @@
       <ns0:c r="P54" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q54" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q54"/>
     </ns0:row>
     <ns0:row r="55" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A55" s="6" t="n">
@@ -7098,9 +6886,7 @@
       <ns0:c r="C55" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D55" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D55" s="1"/>
       <ns0:c r="E55" s="1" t="n">
         <ns0:v>445</ns0:v>
       </ns0:c>
@@ -7137,9 +6923,7 @@
       <ns0:c r="P55" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q55" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q55"/>
     </ns0:row>
     <ns0:row r="56" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A56" s="6" t="n">
@@ -7151,9 +6935,7 @@
       <ns0:c r="C56" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D56" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D56" s="1"/>
       <ns0:c r="E56" s="1" t="n">
         <ns0:v>335.98</ns0:v>
       </ns0:c>
@@ -7190,9 +6972,7 @@
       <ns0:c r="P56" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q56" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q56"/>
     </ns0:row>
     <ns0:row r="57" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A57" s="6" t="n">
@@ -7204,9 +6984,7 @@
       <ns0:c r="C57" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D57" s="1" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c r="D57" s="1"/>
       <ns0:c r="E57" s="1" t="n">
         <ns0:v>328.38</ns0:v>
       </ns0:c>
@@ -7243,9 +7021,7 @@
       <ns0:c r="P57" s="1" t="n">
         <ns0:v>59</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q57" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q57"/>
     </ns0:row>
     <ns0:row r="58" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A58" s="6" t="n">
@@ -7257,9 +7033,7 @@
       <ns0:c r="C58" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D58" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D58" s="1"/>
       <ns0:c r="E58" s="1" t="n">
         <ns0:v>280.95</ns0:v>
       </ns0:c>
@@ -7296,9 +7070,7 @@
       <ns0:c r="P58" s="1" t="n">
         <ns0:v>59</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q58" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q58"/>
     </ns0:row>
     <ns0:row r="59" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A59" s="6" t="n">
@@ -7310,9 +7082,7 @@
       <ns0:c r="C59" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D59" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D59" s="1"/>
       <ns0:c r="E59" s="1" t="n">
         <ns0:v>330.54</ns0:v>
       </ns0:c>
@@ -7349,9 +7119,7 @@
       <ns0:c r="P59" s="1" t="n">
         <ns0:v>59</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q59" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q59"/>
     </ns0:row>
     <ns0:row r="60" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A60" s="6" t="n">
@@ -7363,9 +7131,7 @@
       <ns0:c r="C60" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D60" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D60" s="1"/>
       <ns0:c r="E60" s="1" t="n">
         <ns0:v>391.04</ns0:v>
       </ns0:c>
@@ -7402,9 +7168,7 @@
       <ns0:c r="P60" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q60" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q60"/>
     </ns0:row>
     <ns0:row r="61" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A61" s="6" t="n">
@@ -7416,9 +7180,7 @@
       <ns0:c r="C61" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D61" s="1" t="n">
-        <ns0:v>193.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D61" s="1"/>
       <ns0:c r="E61" s="1" t="n">
         <ns0:v>334.41</ns0:v>
       </ns0:c>
@@ -7455,9 +7217,7 @@
       <ns0:c r="P61" s="1" t="n">
         <ns0:v>61</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q61" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q61"/>
     </ns0:row>
     <ns0:row r="62" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A62" s="6" t="n">
@@ -7469,9 +7229,7 @@
       <ns0:c r="C62" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D62" s="1" t="n">
-        <ns0:v>233.66</ns0:v>
-      </ns0:c>
+      <ns0:c r="D62" s="1"/>
       <ns0:c r="E62" s="1" t="n">
         <ns0:v>331.52</ns0:v>
       </ns0:c>
@@ -7508,9 +7266,7 @@
       <ns0:c r="P62" s="1" t="n">
         <ns0:v>61</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q62" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q62"/>
     </ns0:row>
     <ns0:row r="63" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A63" s="6" t="n">
@@ -7522,9 +7278,7 @@
       <ns0:c r="C63" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D63" s="1" t="n">
-        <ns0:v>233.66</ns0:v>
-      </ns0:c>
+      <ns0:c r="D63" s="1"/>
       <ns0:c r="E63" s="1" t="n">
         <ns0:v>340.13</ns0:v>
       </ns0:c>
@@ -7561,9 +7315,7 @@
       <ns0:c r="P63" s="1" t="n">
         <ns0:v>61</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q63" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q63"/>
     </ns0:row>
     <ns0:row r="64" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A64" s="6" t="n">
@@ -7575,9 +7327,7 @@
       <ns0:c r="C64" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D64" s="1" t="n">
-        <ns0:v>233.66</ns0:v>
-      </ns0:c>
+      <ns0:c r="D64" s="1"/>
       <ns0:c r="E64" s="1" t="n">
         <ns0:v>430</ns0:v>
       </ns0:c>
@@ -7614,9 +7364,7 @@
       <ns0:c r="P64" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q64" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q64"/>
     </ns0:row>
     <ns0:row r="65" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A65" s="6" t="n">
@@ -7628,9 +7376,7 @@
       <ns0:c r="C65" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D65" s="1" t="n">
-        <ns0:v>233.66</ns0:v>
-      </ns0:c>
+      <ns0:c r="D65" s="1"/>
       <ns0:c r="E65" s="1" t="n">
         <ns0:v>477.67</ns0:v>
       </ns0:c>
@@ -7667,9 +7413,7 @@
       <ns0:c r="P65" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q65" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q65"/>
     </ns0:row>
     <ns0:row r="66" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A66" s="6" t="n">
@@ -7681,9 +7425,7 @@
       <ns0:c r="C66" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D66" s="1" t="n">
-        <ns0:v>409.2</ns0:v>
-      </ns0:c>
+      <ns0:c r="D66" s="1"/>
       <ns0:c r="E66" s="1" t="n">
         <ns0:v>700</ns0:v>
       </ns0:c>
@@ -7720,9 +7462,7 @@
       <ns0:c r="P66" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q66" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q66"/>
     </ns0:row>
     <ns0:row r="67" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A67" s="6" t="n">
@@ -7734,9 +7474,7 @@
       <ns0:c r="C67" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D67" s="1" t="n">
-        <ns0:v>409.2</ns0:v>
-      </ns0:c>
+      <ns0:c r="D67" s="1"/>
       <ns0:c r="E67" s="1" t="n">
         <ns0:v>282.82</ns0:v>
       </ns0:c>
@@ -7773,9 +7511,7 @@
       <ns0:c r="P67" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q67" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q67"/>
     </ns0:row>
     <ns0:row r="68" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A68" s="6" t="n">
@@ -7787,9 +7523,7 @@
       <ns0:c r="C68" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D68" s="1" t="n">
-        <ns0:v>409.2</ns0:v>
-      </ns0:c>
+      <ns0:c r="D68" s="1"/>
       <ns0:c r="E68" s="1" t="n">
         <ns0:v>500.39</ns0:v>
       </ns0:c>
@@ -7826,9 +7560,7 @@
       <ns0:c r="P68" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q68" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q68"/>
     </ns0:row>
     <ns0:row r="69" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A69" s="6" t="n">
@@ -7840,9 +7572,7 @@
       <ns0:c r="C69" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D69" s="1" t="n">
-        <ns0:v>409.2</ns0:v>
-      </ns0:c>
+      <ns0:c r="D69" s="1"/>
       <ns0:c r="E69" s="1" t="n">
         <ns0:v>493</ns0:v>
       </ns0:c>
@@ -7879,9 +7609,7 @@
       <ns0:c r="P69" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q69" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q69"/>
     </ns0:row>
     <ns0:row r="70" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A70" s="6" t="n">
@@ -7893,9 +7621,7 @@
       <ns0:c r="C70" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D70" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D70" s="1"/>
       <ns0:c r="E70" s="1" t="n">
         <ns0:v>498.32</ns0:v>
       </ns0:c>
@@ -7932,9 +7658,7 @@
       <ns0:c r="P70" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q70" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q70"/>
     </ns0:row>
     <ns0:row r="71" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A71" s="6" t="n">
@@ -7946,9 +7670,7 @@
       <ns0:c r="C71" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D71" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D71" s="1"/>
       <ns0:c r="E71" s="1" t="n">
         <ns0:v>483.35</ns0:v>
       </ns0:c>
@@ -7985,9 +7707,7 @@
       <ns0:c r="P71" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q71" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q71"/>
     </ns0:row>
     <ns0:row r="72" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A72" s="6" t="n">
@@ -7999,9 +7719,7 @@
       <ns0:c r="C72" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D72" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D72" s="1"/>
       <ns0:c r="E72" s="1" t="n">
         <ns0:v>483.35</ns0:v>
       </ns0:c>
@@ -8038,9 +7756,7 @@
       <ns0:c r="P72" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q72" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q72"/>
     </ns0:row>
     <ns0:row r="73" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A73" s="6" t="n">
@@ -8052,9 +7768,7 @@
       <ns0:c r="C73" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D73" s="1" t="n">
-        <ns0:v>494.23</ns0:v>
-      </ns0:c>
+      <ns0:c r="D73" s="1"/>
       <ns0:c r="E73" s="1" t="n">
         <ns0:v>478.16</ns0:v>
       </ns0:c>
@@ -8091,9 +7805,7 @@
       <ns0:c r="P73" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q73" t="n">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q73"/>
     </ns0:row>
     <ns0:row r="74" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A74" s="6" t="n">
@@ -8105,9 +7817,7 @@
       <ns0:c r="C74" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D74" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
+      <ns0:c r="D74" s="1"/>
       <ns0:c r="E74" s="1" t="n">
         <ns0:v>483.57</ns0:v>
       </ns0:c>
@@ -8144,9 +7854,7 @@
       <ns0:c r="P74" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q74" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q74"/>
     </ns0:row>
     <ns0:row r="75" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A75" s="6" t="n">
@@ -8158,9 +7866,7 @@
       <ns0:c r="C75" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D75" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
+      <ns0:c r="D75" s="1"/>
       <ns0:c r="E75" s="1" t="n">
         <ns0:v>486.8</ns0:v>
       </ns0:c>
@@ -8197,9 +7903,7 @@
       <ns0:c r="P75" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q75" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q75"/>
     </ns0:row>
     <ns0:row r="76" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A76" s="6" t="n">
@@ -8211,9 +7915,7 @@
       <ns0:c r="C76" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D76" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
+      <ns0:c r="D76" s="1"/>
       <ns0:c r="E76" s="1" t="n">
         <ns0:v>469.54</ns0:v>
       </ns0:c>
@@ -8250,9 +7952,7 @@
       <ns0:c r="P76" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q76" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q76"/>
     </ns0:row>
     <ns0:row r="77" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A77" s="6" t="n">
@@ -8264,9 +7964,7 @@
       <ns0:c r="C77" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D77" s="1" t="n">
-        <ns0:v>420</ns0:v>
-      </ns0:c>
+      <ns0:c r="D77" s="1"/>
       <ns0:c r="E77" s="1" t="n">
         <ns0:v>432.58</ns0:v>
       </ns0:c>
@@ -8303,9 +8001,7 @@
       <ns0:c r="P77" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q77" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q77"/>
     </ns0:row>
     <ns0:row r="78" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A78" s="6" t="n">
@@ -8317,9 +8013,7 @@
       <ns0:c r="C78" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D78" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D78" s="1"/>
       <ns0:c r="E78" s="1" t="n">
         <ns0:v>432.58</ns0:v>
       </ns0:c>
@@ -8356,9 +8050,7 @@
       <ns0:c r="P78" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q78" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q78"/>
     </ns0:row>
     <ns0:row r="79" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A79" s="6" t="n">
@@ -8370,9 +8062,7 @@
       <ns0:c r="C79" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D79" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D79" s="1"/>
       <ns0:c r="E79" s="1" t="n">
         <ns0:v>435.26</ns0:v>
       </ns0:c>
@@ -8409,9 +8099,7 @@
       <ns0:c r="P79" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q79" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q79"/>
     </ns0:row>
     <ns0:row r="80" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A80" s="6" t="n">
@@ -8423,9 +8111,7 @@
       <ns0:c r="C80" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D80" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D80" s="1"/>
       <ns0:c r="E80" s="1" t="n">
         <ns0:v>282.82</ns0:v>
       </ns0:c>
@@ -8462,9 +8148,7 @@
       <ns0:c r="P80" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q80" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q80"/>
     </ns0:row>
     <ns0:row r="81" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A81" s="6" t="n">
@@ -8476,9 +8160,7 @@
       <ns0:c r="C81" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D81" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D81" s="1"/>
       <ns0:c r="E81" s="1" t="n">
         <ns0:v>394.48</ns0:v>
       </ns0:c>
@@ -8515,9 +8197,7 @@
       <ns0:c r="P81" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q81" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q81"/>
     </ns0:row>
     <ns0:row r="82" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A82" s="6" t="n">
@@ -8529,9 +8209,7 @@
       <ns0:c r="C82" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D82" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D82" s="1"/>
       <ns0:c r="E82" s="1" t="n">
         <ns0:v>471.57</ns0:v>
       </ns0:c>
@@ -8568,9 +8246,7 @@
       <ns0:c r="P82" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q82" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q82"/>
     </ns0:row>
     <ns0:row r="83" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A83" s="6" t="n">
@@ -8582,9 +8258,7 @@
       <ns0:c r="C83" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D83" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D83" s="1"/>
       <ns0:c r="E83" s="1" t="n">
         <ns0:v>465.52</ns0:v>
       </ns0:c>
@@ -8621,9 +8295,7 @@
       <ns0:c r="P83" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q83" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q83"/>
     </ns0:row>
     <ns0:row r="84" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A84" s="6" t="n">
@@ -8635,9 +8307,7 @@
       <ns0:c r="C84" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D84" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D84" s="1"/>
       <ns0:c r="E84" s="1" t="n">
         <ns0:v>426.3</ns0:v>
       </ns0:c>
@@ -8674,9 +8344,7 @@
       <ns0:c r="P84" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q84" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q84"/>
     </ns0:row>
     <ns0:row r="85" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A85" s="6" t="n">
@@ -8688,9 +8356,7 @@
       <ns0:c r="C85" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D85" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D85" s="1"/>
       <ns0:c r="E85" s="1" t="n">
         <ns0:v>480</ns0:v>
       </ns0:c>
@@ -8727,9 +8393,7 @@
       <ns0:c r="P85" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q85" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q85"/>
     </ns0:row>
     <ns0:row r="86" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A86" s="6" t="n">
@@ -8741,9 +8405,7 @@
       <ns0:c r="C86" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D86" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D86" s="1"/>
       <ns0:c r="E86" s="1" t="n">
         <ns0:v>480</ns0:v>
       </ns0:c>
@@ -8780,9 +8442,7 @@
       <ns0:c r="P86" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q86" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q86"/>
     </ns0:row>
     <ns0:row r="87" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A87" s="6" t="n">
@@ -8794,9 +8454,7 @@
       <ns0:c r="C87" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D87" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D87" s="1"/>
       <ns0:c r="E87" s="1" t="n">
         <ns0:v>469</ns0:v>
       </ns0:c>
@@ -8833,9 +8491,7 @@
       <ns0:c r="P87" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q87" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q87"/>
     </ns0:row>
     <ns0:row r="88" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A88" s="6" t="n">
@@ -8847,9 +8503,7 @@
       <ns0:c r="C88" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D88" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D88" s="1"/>
       <ns0:c r="E88" s="1" t="n">
         <ns0:v>426.3</ns0:v>
       </ns0:c>
@@ -8886,9 +8540,7 @@
       <ns0:c r="P88" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q88" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q88"/>
     </ns0:row>
     <ns0:row r="89" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A89" s="6" t="n">
@@ -8900,9 +8552,7 @@
       <ns0:c r="C89" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D89" s="1" t="n">
-        <ns0:v>390.61</ns0:v>
-      </ns0:c>
+      <ns0:c r="D89" s="1"/>
       <ns0:c r="E89" s="1" t="n">
         <ns0:v>404.2</ns0:v>
       </ns0:c>
@@ -8939,9 +8589,7 @@
       <ns0:c r="P89" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q89" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q89"/>
     </ns0:row>
     <ns0:row r="90" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A90" s="6" t="n">
@@ -8953,9 +8601,7 @@
       <ns0:c r="C90" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D90" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D90" s="1"/>
       <ns0:c r="E90" s="1" t="n">
         <ns0:v>422.45</ns0:v>
       </ns0:c>
@@ -8992,9 +8638,7 @@
       <ns0:c r="P90" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q90" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q90"/>
     </ns0:row>
     <ns0:row r="91" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A91" s="6" t="n">
@@ -9006,9 +8650,7 @@
       <ns0:c r="C91" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D91" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D91" s="1"/>
       <ns0:c r="E91" s="1" t="n">
         <ns0:v>402.54</ns0:v>
       </ns0:c>
@@ -9045,9 +8687,7 @@
       <ns0:c r="P91" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q91" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q91"/>
     </ns0:row>
     <ns0:row r="92" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A92" s="6" t="n">
@@ -9059,9 +8699,7 @@
       <ns0:c r="C92" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D92" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D92" s="1"/>
       <ns0:c r="E92" s="1" t="n">
         <ns0:v>334.67</ns0:v>
       </ns0:c>
@@ -9098,9 +8736,7 @@
       <ns0:c r="P92" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q92" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q92"/>
     </ns0:row>
     <ns0:row r="93" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A93" s="6" t="n">
@@ -9112,9 +8748,7 @@
       <ns0:c r="C93" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D93" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D93" s="1"/>
       <ns0:c r="E93" s="1" t="n">
         <ns0:v>417.22</ns0:v>
       </ns0:c>
@@ -9151,9 +8785,7 @@
       <ns0:c r="P93" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q93" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q93"/>
     </ns0:row>
     <ns0:row r="94" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A94" s="6" t="n">
@@ -9165,9 +8797,7 @@
       <ns0:c r="C94" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D94" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D94" s="1"/>
       <ns0:c r="E94" s="1" t="n">
         <ns0:v>469.54</ns0:v>
       </ns0:c>
@@ -9204,9 +8834,7 @@
       <ns0:c r="P94" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q94" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q94"/>
     </ns0:row>
     <ns0:row r="95" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A95" s="6" t="n">
@@ -9218,9 +8846,7 @@
       <ns0:c r="C95" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D95" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D95" s="1"/>
       <ns0:c r="E95" s="1" t="n">
         <ns0:v>423.26</ns0:v>
       </ns0:c>
@@ -9257,9 +8883,7 @@
       <ns0:c r="P95" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q95" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q95"/>
     </ns0:row>
     <ns0:row r="96" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A96" s="6" t="n">
@@ -9271,9 +8895,7 @@
       <ns0:c r="C96" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D96" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D96" s="1"/>
       <ns0:c r="E96" s="1" t="n">
         <ns0:v>404.2</ns0:v>
       </ns0:c>
@@ -9310,9 +8932,7 @@
       <ns0:c r="P96" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q96" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q96"/>
     </ns0:row>
     <ns0:row r="97" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A97" s="6" t="n">
@@ -9326,9 +8946,7 @@
       <ns0:c r="C97" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D97" s="1" t="n">
-        <ns0:v>330</ns0:v>
-      </ns0:c>
+      <ns0:c r="D97" s="1"/>
       <ns0:c r="E97" s="1" t="n">
         <ns0:v>402.8</ns0:v>
       </ns0:c>
@@ -9365,9 +8983,7 @@
       <ns0:c r="P97" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q97" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
+      <ns0:c s="1" r="Q97"/>
     </ns0:row>
   </ns0:sheetData>
   <conditionalFormatting sqref="A1:B1">

--- a/review-results/河北实时运行及市场出清数据-20261015.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20261015.xlsx
@@ -4289,7 +4289,9 @@
       <ns0:c r="C2" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D2" s="1"/>
+      <ns0:c r="D2" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E2" s="1" t="n">
         <ns0:v>389.39</ns0:v>
       </ns0:c>
@@ -4326,7 +4328,9 @@
       <ns0:c r="P2" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q2"/>
+      <ns0:c s="1" r="Q2" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="3" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A3" s="6" t="n">
@@ -4338,7 +4342,9 @@
       <ns0:c r="C3" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D3" s="1"/>
+      <ns0:c r="D3" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E3" s="1" t="n">
         <ns0:v>390.61</ns0:v>
       </ns0:c>
@@ -4375,7 +4381,9 @@
       <ns0:c r="P3" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q3"/>
+      <ns0:c s="1" r="Q3" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="4" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A4" s="6" t="n">
@@ -4387,7 +4395,9 @@
       <ns0:c r="C4" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D4" s="1"/>
+      <ns0:c r="D4" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E4" s="1" t="n">
         <ns0:v>394.48</ns0:v>
       </ns0:c>
@@ -4424,7 +4434,9 @@
       <ns0:c r="P4" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q4"/>
+      <ns0:c s="1" r="Q4" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="5" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A5" s="6" t="n">
@@ -4436,7 +4448,9 @@
       <ns0:c r="C5" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D5" s="1"/>
+      <ns0:c r="D5" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E5" s="1" t="n">
         <ns0:v>390.04</ns0:v>
       </ns0:c>
@@ -4473,7 +4487,9 @@
       <ns0:c r="P5" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q5"/>
+      <ns0:c s="1" r="Q5" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="6" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A6" s="6" t="n">
@@ -4485,7 +4501,9 @@
       <ns0:c r="C6" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D6" s="1"/>
+      <ns0:c r="D6" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E6" s="1" t="n">
         <ns0:v>390.61</ns0:v>
       </ns0:c>
@@ -4522,7 +4540,9 @@
       <ns0:c r="P6" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q6"/>
+      <ns0:c s="1" r="Q6" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="7" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A7" s="6" t="n">
@@ -4534,7 +4554,9 @@
       <ns0:c r="C7" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D7" s="1"/>
+      <ns0:c r="D7" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E7" s="1" t="n">
         <ns0:v>390.61</ns0:v>
       </ns0:c>
@@ -4571,7 +4593,9 @@
       <ns0:c r="P7" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q7"/>
+      <ns0:c s="1" r="Q7" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="8" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A8" s="6" t="n">
@@ -4583,7 +4607,9 @@
       <ns0:c r="C8" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D8" s="1"/>
+      <ns0:c r="D8" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E8" s="1" t="n">
         <ns0:v>338.23</ns0:v>
       </ns0:c>
@@ -4620,7 +4646,9 @@
       <ns0:c r="P8" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q8"/>
+      <ns0:c s="1" r="Q8" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="9" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A9" s="6" t="n">
@@ -4632,7 +4660,9 @@
       <ns0:c r="C9" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D9" s="1"/>
+      <ns0:c r="D9" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E9" s="1" t="n">
         <ns0:v>334.67</ns0:v>
       </ns0:c>
@@ -4669,7 +4699,9 @@
       <ns0:c r="P9" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q9"/>
+      <ns0:c s="1" r="Q9" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="10" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A10" s="6" t="n">
@@ -4681,7 +4713,9 @@
       <ns0:c r="C10" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D10" s="1"/>
+      <ns0:c r="D10" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E10" s="1" t="n">
         <ns0:v>475.19</ns0:v>
       </ns0:c>
@@ -4718,7 +4752,9 @@
       <ns0:c r="P10" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q10"/>
+      <ns0:c s="1" r="Q10" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="11" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A11" s="6" t="n">
@@ -4730,7 +4766,9 @@
       <ns0:c r="C11" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D11" s="1"/>
+      <ns0:c r="D11" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E11" s="1" t="n">
         <ns0:v>400.57</ns0:v>
       </ns0:c>
@@ -4767,7 +4805,9 @@
       <ns0:c r="P11" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q11"/>
+      <ns0:c s="1" r="Q11" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="12" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A12" s="6" t="n">
@@ -4779,7 +4819,9 @@
       <ns0:c r="C12" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D12" s="1"/>
+      <ns0:c r="D12" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E12" s="1" t="n">
         <ns0:v>391.04</ns0:v>
       </ns0:c>
@@ -4816,7 +4858,9 @@
       <ns0:c r="P12" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q12"/>
+      <ns0:c s="1" r="Q12" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="13" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A13" s="6" t="n">
@@ -4828,7 +4872,9 @@
       <ns0:c r="C13" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D13" s="1"/>
+      <ns0:c r="D13" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E13" s="1" t="n">
         <ns0:v>394.48</ns0:v>
       </ns0:c>
@@ -4865,7 +4911,9 @@
       <ns0:c r="P13" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q13"/>
+      <ns0:c s="1" r="Q13" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="14" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A14" s="6" t="n">
@@ -4877,7 +4925,9 @@
       <ns0:c r="C14" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D14" s="1"/>
+      <ns0:c r="D14" s="1" t="n">
+        <ns0:v>389</ns0:v>
+      </ns0:c>
       <ns0:c r="E14" s="1" t="n">
         <ns0:v>423.26</ns0:v>
       </ns0:c>
@@ -4914,7 +4964,9 @@
       <ns0:c r="P14" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q14"/>
+      <ns0:c s="1" r="Q14" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="15" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A15" s="6" t="n">
@@ -4926,7 +4978,9 @@
       <ns0:c r="C15" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D15" s="1"/>
+      <ns0:c r="D15" s="1" t="n">
+        <ns0:v>389</ns0:v>
+      </ns0:c>
       <ns0:c r="E15" s="1" t="n">
         <ns0:v>425.14</ns0:v>
       </ns0:c>
@@ -4963,7 +5017,9 @@
       <ns0:c r="P15" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q15"/>
+      <ns0:c s="1" r="Q15" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="16" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A16" s="6" t="n">
@@ -4975,7 +5031,9 @@
       <ns0:c r="C16" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D16" s="1"/>
+      <ns0:c r="D16" s="1" t="n">
+        <ns0:v>389</ns0:v>
+      </ns0:c>
       <ns0:c r="E16" s="1" t="n">
         <ns0:v>469.48</ns0:v>
       </ns0:c>
@@ -5012,7 +5070,9 @@
       <ns0:c r="P16" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q16"/>
+      <ns0:c s="1" r="Q16" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="17" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A17" s="6" t="n">
@@ -5024,7 +5084,9 @@
       <ns0:c r="C17" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D17" s="1"/>
+      <ns0:c r="D17" s="1" t="n">
+        <ns0:v>389</ns0:v>
+      </ns0:c>
       <ns0:c r="E17" s="1" t="n">
         <ns0:v>445</ns0:v>
       </ns0:c>
@@ -5061,7 +5123,9 @@
       <ns0:c r="P17" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q17"/>
+      <ns0:c s="1" r="Q17" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="18" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A18" s="6" t="n">
@@ -5073,7 +5137,9 @@
       <ns0:c r="C18" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D18" s="1"/>
+      <ns0:c r="D18" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E18" s="1" t="n">
         <ns0:v>470.5</ns0:v>
       </ns0:c>
@@ -5110,7 +5176,9 @@
       <ns0:c r="P18" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q18"/>
+      <ns0:c s="1" r="Q18" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="19" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A19" s="6" t="n">
@@ -5122,7 +5190,9 @@
       <ns0:c r="C19" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D19" s="1"/>
+      <ns0:c r="D19" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E19" s="1" t="n">
         <ns0:v>469.1</ns0:v>
       </ns0:c>
@@ -5159,7 +5229,9 @@
       <ns0:c r="P19" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q19"/>
+      <ns0:c s="1" r="Q19" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="20" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A20" s="6" t="n">
@@ -5171,7 +5243,9 @@
       <ns0:c r="C20" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D20" s="1"/>
+      <ns0:c r="D20" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E20" s="1" t="n">
         <ns0:v>469.1</ns0:v>
       </ns0:c>
@@ -5208,7 +5282,9 @@
       <ns0:c r="P20" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q20"/>
+      <ns0:c s="1" r="Q20" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="21" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A21" s="6" t="n">
@@ -5220,7 +5296,9 @@
       <ns0:c r="C21" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D21" s="1"/>
+      <ns0:c r="D21" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E21" s="1" t="n">
         <ns0:v>435.26</ns0:v>
       </ns0:c>
@@ -5257,7 +5335,9 @@
       <ns0:c r="P21" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q21"/>
+      <ns0:c s="1" r="Q21" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="22" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A22" s="6" t="n">
@@ -5269,7 +5349,9 @@
       <ns0:c r="C22" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D22" s="1"/>
+      <ns0:c r="D22" s="1" t="n">
+        <ns0:v>398.79</ns0:v>
+      </ns0:c>
       <ns0:c r="E22" s="1" t="n">
         <ns0:v>433.17</ns0:v>
       </ns0:c>
@@ -5306,7 +5388,9 @@
       <ns0:c r="P22" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q22"/>
+      <ns0:c s="1" r="Q22" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="23" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A23" s="6" t="n">
@@ -5318,7 +5402,9 @@
       <ns0:c r="C23" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D23" s="1"/>
+      <ns0:c r="D23" s="1" t="n">
+        <ns0:v>398.79</ns0:v>
+      </ns0:c>
       <ns0:c r="E23" s="1" t="n">
         <ns0:v>465.52</ns0:v>
       </ns0:c>
@@ -5355,7 +5441,9 @@
       <ns0:c r="P23" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q23"/>
+      <ns0:c s="1" r="Q23" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="24" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A24" s="6" t="n">
@@ -5367,7 +5455,9 @@
       <ns0:c r="C24" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D24" s="1"/>
+      <ns0:c r="D24" s="1" t="n">
+        <ns0:v>398.79</ns0:v>
+      </ns0:c>
       <ns0:c r="E24" s="1" t="n">
         <ns0:v>432.58</ns0:v>
       </ns0:c>
@@ -5404,7 +5494,9 @@
       <ns0:c r="P24" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q24"/>
+      <ns0:c s="1" r="Q24" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="25" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A25" s="6" t="n">
@@ -5416,7 +5508,9 @@
       <ns0:c r="C25" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D25" s="1"/>
+      <ns0:c r="D25" s="1" t="n">
+        <ns0:v>398.79</ns0:v>
+      </ns0:c>
       <ns0:c r="E25" s="1" t="n">
         <ns0:v>473.23</ns0:v>
       </ns0:c>
@@ -5453,7 +5547,9 @@
       <ns0:c r="P25" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q25"/>
+      <ns0:c s="1" r="Q25" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="26" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A26" s="6" t="n">
@@ -5465,7 +5561,9 @@
       <ns0:c r="C26" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D26" s="1"/>
+      <ns0:c r="D26" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E26" s="1" t="n">
         <ns0:v>475.2</ns0:v>
       </ns0:c>
@@ -5502,7 +5600,9 @@
       <ns0:c r="P26" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q26"/>
+      <ns0:c s="1" r="Q26" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="27" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A27" s="6" t="n">
@@ -5514,7 +5614,9 @@
       <ns0:c r="C27" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D27" s="1"/>
+      <ns0:c r="D27" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E27" s="1" t="n">
         <ns0:v>425.45</ns0:v>
       </ns0:c>
@@ -5551,7 +5653,9 @@
       <ns0:c r="P27" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q27"/>
+      <ns0:c s="1" r="Q27" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="28" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A28" s="6" t="n">
@@ -5563,7 +5667,9 @@
       <ns0:c r="C28" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D28" s="1"/>
+      <ns0:c r="D28" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E28" s="1" t="n">
         <ns0:v>424.07</ns0:v>
       </ns0:c>
@@ -5600,7 +5706,9 @@
       <ns0:c r="P28" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q28"/>
+      <ns0:c s="1" r="Q28" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="29" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A29" s="6" t="n">
@@ -5612,7 +5720,9 @@
       <ns0:c r="C29" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D29" s="1"/>
+      <ns0:c r="D29" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E29" s="1" t="n">
         <ns0:v>433.17</ns0:v>
       </ns0:c>
@@ -5649,7 +5759,9 @@
       <ns0:c r="P29" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q29"/>
+      <ns0:c s="1" r="Q29" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="30" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A30" s="6" t="n">
@@ -5661,7 +5773,9 @@
       <ns0:c r="C30" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D30" s="1"/>
+      <ns0:c r="D30" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E30" s="1" t="n">
         <ns0:v>475.19</ns0:v>
       </ns0:c>
@@ -5698,7 +5812,9 @@
       <ns0:c r="P30" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q30"/>
+      <ns0:c s="1" r="Q30" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="31" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A31" s="6" t="n">
@@ -5710,7 +5826,9 @@
       <ns0:c r="C31" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D31" s="1"/>
+      <ns0:c r="D31" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E31" s="1" t="n">
         <ns0:v>465.52</ns0:v>
       </ns0:c>
@@ -5747,7 +5865,9 @@
       <ns0:c r="P31" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q31"/>
+      <ns0:c s="1" r="Q31" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="32" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A32" s="6" t="n">
@@ -5759,7 +5879,9 @@
       <ns0:c r="C32" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D32" s="1"/>
+      <ns0:c r="D32" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E32" s="1" t="n">
         <ns0:v>425.45</ns0:v>
       </ns0:c>
@@ -5796,7 +5918,9 @@
       <ns0:c r="P32" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q32"/>
+      <ns0:c s="1" r="Q32" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="33" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A33" s="6" t="n">
@@ -5808,7 +5932,9 @@
       <ns0:c r="C33" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D33" s="1"/>
+      <ns0:c r="D33" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E33" s="1" t="n">
         <ns0:v>343.05</ns0:v>
       </ns0:c>
@@ -5845,7 +5971,9 @@
       <ns0:c r="P33" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q33"/>
+      <ns0:c s="1" r="Q33" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="34" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A34" s="6" t="n">
@@ -5857,7 +5985,9 @@
       <ns0:c r="C34" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D34" s="1"/>
+      <ns0:c r="D34" s="1" t="n">
+        <ns0:v>193</ns0:v>
+      </ns0:c>
       <ns0:c r="E34" s="1" t="n">
         <ns0:v>343.05</ns0:v>
       </ns0:c>
@@ -5894,7 +6024,9 @@
       <ns0:c r="P34" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q34"/>
+      <ns0:c s="1" r="Q34" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="35" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A35" s="6" t="n">
@@ -5906,7 +6038,9 @@
       <ns0:c r="C35" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D35" s="1"/>
+      <ns0:c r="D35" s="1" t="n">
+        <ns0:v>193</ns0:v>
+      </ns0:c>
       <ns0:c r="E35" s="1" t="n">
         <ns0:v>334.41</ns0:v>
       </ns0:c>
@@ -5943,7 +6077,9 @@
       <ns0:c r="P35" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q35"/>
+      <ns0:c s="1" r="Q35" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="36" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A36" s="6" t="n">
@@ -5955,7 +6091,9 @@
       <ns0:c r="C36" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D36" s="1"/>
+      <ns0:c r="D36" s="1" t="n">
+        <ns0:v>193</ns0:v>
+      </ns0:c>
       <ns0:c r="E36" s="1" t="n">
         <ns0:v>276.08</ns0:v>
       </ns0:c>
@@ -5992,7 +6130,9 @@
       <ns0:c r="P36" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q36"/>
+      <ns0:c s="1" r="Q36" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="37" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A37" s="6" t="n">
@@ -6004,7 +6144,9 @@
       <ns0:c r="C37" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D37" s="1"/>
+      <ns0:c r="D37" s="1" t="n">
+        <ns0:v>193</ns0:v>
+      </ns0:c>
       <ns0:c r="E37" s="1" t="n">
         <ns0:v>235.41</ns0:v>
       </ns0:c>
@@ -6041,7 +6183,9 @@
       <ns0:c r="P37" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q37"/>
+      <ns0:c s="1" r="Q37" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="38" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A38" s="6" t="n">
@@ -6053,7 +6197,9 @@
       <ns0:c r="C38" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D38" s="1"/>
+      <ns0:c r="D38" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E38" s="1" t="n">
         <ns0:v>199.14</ns0:v>
       </ns0:c>
@@ -6090,7 +6236,9 @@
       <ns0:c r="P38" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q38"/>
+      <ns0:c s="1" r="Q38" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="39" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A39" s="6" t="n">
@@ -6102,7 +6250,9 @@
       <ns0:c r="C39" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D39" s="1"/>
+      <ns0:c r="D39" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E39" s="1" t="n">
         <ns0:v>280</ns0:v>
       </ns0:c>
@@ -6139,7 +6289,9 @@
       <ns0:c r="P39" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q39"/>
+      <ns0:c s="1" r="Q39" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="40" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A40" s="6" t="n">
@@ -6151,7 +6303,9 @@
       <ns0:c r="C40" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D40" s="1"/>
+      <ns0:c r="D40" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E40" s="1" t="n">
         <ns0:v>330.54</ns0:v>
       </ns0:c>
@@ -6188,7 +6342,9 @@
       <ns0:c r="P40" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q40"/>
+      <ns0:c s="1" r="Q40" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="41" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A41" s="6" t="n">
@@ -6200,7 +6356,9 @@
       <ns0:c r="C41" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D41" s="1"/>
+      <ns0:c r="D41" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E41" s="1" t="n">
         <ns0:v>278.94</ns0:v>
       </ns0:c>
@@ -6237,7 +6395,9 @@
       <ns0:c r="P41" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q41"/>
+      <ns0:c s="1" r="Q41" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="42" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A42" s="6" t="n">
@@ -6249,7 +6409,9 @@
       <ns0:c r="C42" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D42" s="1"/>
+      <ns0:c r="D42" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E42" s="1" t="n">
         <ns0:v>335.98</ns0:v>
       </ns0:c>
@@ -6286,7 +6448,9 @@
       <ns0:c r="P42" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q42"/>
+      <ns0:c s="1" r="Q42" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="43" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A43" s="6" t="n">
@@ -6298,7 +6462,9 @@
       <ns0:c r="C43" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D43" s="1"/>
+      <ns0:c r="D43" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E43" s="1" t="n">
         <ns0:v>330.01</ns0:v>
       </ns0:c>
@@ -6335,7 +6501,9 @@
       <ns0:c r="P43" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q43"/>
+      <ns0:c s="1" r="Q43" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="44" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A44" s="6" t="n">
@@ -6347,7 +6515,9 @@
       <ns0:c r="C44" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D44" s="1"/>
+      <ns0:c r="D44" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E44" s="1" t="n">
         <ns0:v>334.67</ns0:v>
       </ns0:c>
@@ -6384,7 +6554,9 @@
       <ns0:c r="P44" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q44"/>
+      <ns0:c s="1" r="Q44" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="45" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A45" s="6" t="n">
@@ -6396,7 +6568,9 @@
       <ns0:c r="C45" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D45" s="1"/>
+      <ns0:c r="D45" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E45" s="1" t="n">
         <ns0:v>335.98</ns0:v>
       </ns0:c>
@@ -6433,7 +6607,9 @@
       <ns0:c r="P45" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q45"/>
+      <ns0:c s="1" r="Q45" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="46" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A46" s="6" t="n">
@@ -6445,7 +6621,9 @@
       <ns0:c r="C46" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D46" s="1"/>
+      <ns0:c r="D46" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E46" s="1" t="n">
         <ns0:v>203.89</ns0:v>
       </ns0:c>
@@ -6482,7 +6660,9 @@
       <ns0:c r="P46" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q46"/>
+      <ns0:c s="1" r="Q46" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="47" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A47" s="6" t="n">
@@ -6494,7 +6674,9 @@
       <ns0:c r="C47" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D47" s="1"/>
+      <ns0:c r="D47" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E47" s="1" t="n">
         <ns0:v>330.79</ns0:v>
       </ns0:c>
@@ -6531,7 +6713,9 @@
       <ns0:c r="P47" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q47"/>
+      <ns0:c s="1" r="Q47" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="48" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A48" s="6" t="n">
@@ -6543,7 +6727,9 @@
       <ns0:c r="C48" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D48" s="1"/>
+      <ns0:c r="D48" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E48" s="1" t="n">
         <ns0:v>280.95</ns0:v>
       </ns0:c>
@@ -6580,7 +6766,9 @@
       <ns0:c r="P48" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q48"/>
+      <ns0:c s="1" r="Q48" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="49" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A49" s="6" t="n">
@@ -6592,7 +6780,9 @@
       <ns0:c r="C49" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D49" s="1"/>
+      <ns0:c r="D49" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E49" s="1" t="n">
         <ns0:v>206.83</ns0:v>
       </ns0:c>
@@ -6629,7 +6819,9 @@
       <ns0:c r="P49" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q49"/>
+      <ns0:c s="1" r="Q49" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="50" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A50" s="6" t="n">
@@ -6641,7 +6833,9 @@
       <ns0:c r="C50" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D50" s="1"/>
+      <ns0:c r="D50" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E50" s="1" t="n">
         <ns0:v>328.38</ns0:v>
       </ns0:c>
@@ -6678,7 +6872,9 @@
       <ns0:c r="P50" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q50"/>
+      <ns0:c s="1" r="Q50" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="51" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A51" s="6" t="n">
@@ -6690,7 +6886,9 @@
       <ns0:c r="C51" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D51" s="1"/>
+      <ns0:c r="D51" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E51" s="1" t="n">
         <ns0:v>226.8</ns0:v>
       </ns0:c>
@@ -6727,7 +6925,9 @@
       <ns0:c r="P51" s="1" t="n">
         <ns0:v>56</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q51"/>
+      <ns0:c s="1" r="Q51" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="52" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A52" s="6" t="n">
@@ -6739,7 +6939,9 @@
       <ns0:c r="C52" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D52" s="1"/>
+      <ns0:c r="D52" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E52" s="1" t="n">
         <ns0:v>231.86</ns0:v>
       </ns0:c>
@@ -6776,7 +6978,9 @@
       <ns0:c r="P52" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q52"/>
+      <ns0:c s="1" r="Q52" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="53" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A53" s="6" t="n">
@@ -6788,7 +6992,9 @@
       <ns0:c r="C53" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D53" s="1"/>
+      <ns0:c r="D53" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E53" s="1" t="n">
         <ns0:v>330.79</ns0:v>
       </ns0:c>
@@ -6825,7 +7031,9 @@
       <ns0:c r="P53" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q53"/>
+      <ns0:c s="1" r="Q53" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="54" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A54" s="6" t="n">
@@ -6837,7 +7045,9 @@
       <ns0:c r="C54" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D54" s="1"/>
+      <ns0:c r="D54" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E54" s="1" t="n">
         <ns0:v>237</ns0:v>
       </ns0:c>
@@ -6874,7 +7084,9 @@
       <ns0:c r="P54" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q54"/>
+      <ns0:c s="1" r="Q54" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="55" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A55" s="6" t="n">
@@ -6886,7 +7098,9 @@
       <ns0:c r="C55" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D55" s="1"/>
+      <ns0:c r="D55" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E55" s="1" t="n">
         <ns0:v>445</ns0:v>
       </ns0:c>
@@ -6923,7 +7137,9 @@
       <ns0:c r="P55" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q55"/>
+      <ns0:c s="1" r="Q55" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="56" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A56" s="6" t="n">
@@ -6935,7 +7151,9 @@
       <ns0:c r="C56" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D56" s="1"/>
+      <ns0:c r="D56" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E56" s="1" t="n">
         <ns0:v>335.98</ns0:v>
       </ns0:c>
@@ -6972,7 +7190,9 @@
       <ns0:c r="P56" s="1" t="n">
         <ns0:v>57</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q56"/>
+      <ns0:c s="1" r="Q56" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="57" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A57" s="6" t="n">
@@ -6984,7 +7204,9 @@
       <ns0:c r="C57" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D57" s="1"/>
+      <ns0:c r="D57" s="1" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
       <ns0:c r="E57" s="1" t="n">
         <ns0:v>328.38</ns0:v>
       </ns0:c>
@@ -7021,7 +7243,9 @@
       <ns0:c r="P57" s="1" t="n">
         <ns0:v>59</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q57"/>
+      <ns0:c s="1" r="Q57" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="58" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A58" s="6" t="n">
@@ -7033,7 +7257,9 @@
       <ns0:c r="C58" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D58" s="1"/>
+      <ns0:c r="D58" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E58" s="1" t="n">
         <ns0:v>280.95</ns0:v>
       </ns0:c>
@@ -7070,7 +7296,9 @@
       <ns0:c r="P58" s="1" t="n">
         <ns0:v>59</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q58"/>
+      <ns0:c s="1" r="Q58" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="59" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A59" s="6" t="n">
@@ -7082,7 +7310,9 @@
       <ns0:c r="C59" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D59" s="1"/>
+      <ns0:c r="D59" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E59" s="1" t="n">
         <ns0:v>330.54</ns0:v>
       </ns0:c>
@@ -7119,7 +7349,9 @@
       <ns0:c r="P59" s="1" t="n">
         <ns0:v>59</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q59"/>
+      <ns0:c s="1" r="Q59" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="60" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A60" s="6" t="n">
@@ -7131,7 +7363,9 @@
       <ns0:c r="C60" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D60" s="1"/>
+      <ns0:c r="D60" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E60" s="1" t="n">
         <ns0:v>391.04</ns0:v>
       </ns0:c>
@@ -7168,7 +7402,9 @@
       <ns0:c r="P60" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q60"/>
+      <ns0:c s="1" r="Q60" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="61" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A61" s="6" t="n">
@@ -7180,7 +7416,9 @@
       <ns0:c r="C61" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D61" s="1"/>
+      <ns0:c r="D61" s="1" t="n">
+        <ns0:v>193.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E61" s="1" t="n">
         <ns0:v>334.41</ns0:v>
       </ns0:c>
@@ -7217,7 +7455,9 @@
       <ns0:c r="P61" s="1" t="n">
         <ns0:v>61</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q61"/>
+      <ns0:c s="1" r="Q61" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="62" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A62" s="6" t="n">
@@ -7229,7 +7469,9 @@
       <ns0:c r="C62" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D62" s="1"/>
+      <ns0:c r="D62" s="1" t="n">
+        <ns0:v>233.66</ns0:v>
+      </ns0:c>
       <ns0:c r="E62" s="1" t="n">
         <ns0:v>331.52</ns0:v>
       </ns0:c>
@@ -7266,7 +7508,9 @@
       <ns0:c r="P62" s="1" t="n">
         <ns0:v>61</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q62"/>
+      <ns0:c s="1" r="Q62" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="63" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A63" s="6" t="n">
@@ -7278,7 +7522,9 @@
       <ns0:c r="C63" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D63" s="1"/>
+      <ns0:c r="D63" s="1" t="n">
+        <ns0:v>233.66</ns0:v>
+      </ns0:c>
       <ns0:c r="E63" s="1" t="n">
         <ns0:v>340.13</ns0:v>
       </ns0:c>
@@ -7315,7 +7561,9 @@
       <ns0:c r="P63" s="1" t="n">
         <ns0:v>61</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q63"/>
+      <ns0:c s="1" r="Q63" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="64" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A64" s="6" t="n">
@@ -7327,7 +7575,9 @@
       <ns0:c r="C64" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D64" s="1"/>
+      <ns0:c r="D64" s="1" t="n">
+        <ns0:v>233.66</ns0:v>
+      </ns0:c>
       <ns0:c r="E64" s="1" t="n">
         <ns0:v>430</ns0:v>
       </ns0:c>
@@ -7364,7 +7614,9 @@
       <ns0:c r="P64" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q64"/>
+      <ns0:c s="1" r="Q64" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="65" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A65" s="6" t="n">
@@ -7376,7 +7628,9 @@
       <ns0:c r="C65" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D65" s="1"/>
+      <ns0:c r="D65" s="1" t="n">
+        <ns0:v>233.66</ns0:v>
+      </ns0:c>
       <ns0:c r="E65" s="1" t="n">
         <ns0:v>477.67</ns0:v>
       </ns0:c>
@@ -7413,7 +7667,9 @@
       <ns0:c r="P65" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q65"/>
+      <ns0:c s="1" r="Q65" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="66" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A66" s="6" t="n">
@@ -7425,7 +7681,9 @@
       <ns0:c r="C66" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D66" s="1"/>
+      <ns0:c r="D66" s="1" t="n">
+        <ns0:v>409.2</ns0:v>
+      </ns0:c>
       <ns0:c r="E66" s="1" t="n">
         <ns0:v>700</ns0:v>
       </ns0:c>
@@ -7462,7 +7720,9 @@
       <ns0:c r="P66" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q66"/>
+      <ns0:c s="1" r="Q66" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="67" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A67" s="6" t="n">
@@ -7474,7 +7734,9 @@
       <ns0:c r="C67" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D67" s="1"/>
+      <ns0:c r="D67" s="1" t="n">
+        <ns0:v>409.2</ns0:v>
+      </ns0:c>
       <ns0:c r="E67" s="1" t="n">
         <ns0:v>282.82</ns0:v>
       </ns0:c>
@@ -7511,7 +7773,9 @@
       <ns0:c r="P67" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q67"/>
+      <ns0:c s="1" r="Q67" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="68" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A68" s="6" t="n">
@@ -7523,7 +7787,9 @@
       <ns0:c r="C68" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D68" s="1"/>
+      <ns0:c r="D68" s="1" t="n">
+        <ns0:v>409.2</ns0:v>
+      </ns0:c>
       <ns0:c r="E68" s="1" t="n">
         <ns0:v>500.39</ns0:v>
       </ns0:c>
@@ -7560,7 +7826,9 @@
       <ns0:c r="P68" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q68"/>
+      <ns0:c s="1" r="Q68" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="69" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A69" s="6" t="n">
@@ -7572,7 +7840,9 @@
       <ns0:c r="C69" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D69" s="1"/>
+      <ns0:c r="D69" s="1" t="n">
+        <ns0:v>409.2</ns0:v>
+      </ns0:c>
       <ns0:c r="E69" s="1" t="n">
         <ns0:v>493</ns0:v>
       </ns0:c>
@@ -7609,7 +7879,9 @@
       <ns0:c r="P69" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q69"/>
+      <ns0:c s="1" r="Q69" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="70" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A70" s="6" t="n">
@@ -7621,7 +7893,9 @@
       <ns0:c r="C70" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D70" s="1"/>
+      <ns0:c r="D70" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E70" s="1" t="n">
         <ns0:v>498.32</ns0:v>
       </ns0:c>
@@ -7658,7 +7932,9 @@
       <ns0:c r="P70" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q70"/>
+      <ns0:c s="1" r="Q70" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="71" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A71" s="6" t="n">
@@ -7670,7 +7946,9 @@
       <ns0:c r="C71" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D71" s="1"/>
+      <ns0:c r="D71" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E71" s="1" t="n">
         <ns0:v>483.35</ns0:v>
       </ns0:c>
@@ -7707,7 +7985,9 @@
       <ns0:c r="P71" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q71"/>
+      <ns0:c s="1" r="Q71" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="72" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A72" s="6" t="n">
@@ -7719,7 +7999,9 @@
       <ns0:c r="C72" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D72" s="1"/>
+      <ns0:c r="D72" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E72" s="1" t="n">
         <ns0:v>483.35</ns0:v>
       </ns0:c>
@@ -7756,7 +8038,9 @@
       <ns0:c r="P72" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q72"/>
+      <ns0:c s="1" r="Q72" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="73" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A73" s="6" t="n">
@@ -7768,7 +8052,9 @@
       <ns0:c r="C73" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D73" s="1"/>
+      <ns0:c r="D73" s="1" t="n">
+        <ns0:v>494.23</ns0:v>
+      </ns0:c>
       <ns0:c r="E73" s="1" t="n">
         <ns0:v>478.16</ns0:v>
       </ns0:c>
@@ -7805,7 +8091,9 @@
       <ns0:c r="P73" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q73"/>
+      <ns0:c s="1" r="Q73" t="n">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="74" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A74" s="6" t="n">
@@ -7817,7 +8105,9 @@
       <ns0:c r="C74" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D74" s="1"/>
+      <ns0:c r="D74" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
       <ns0:c r="E74" s="1" t="n">
         <ns0:v>483.57</ns0:v>
       </ns0:c>
@@ -7854,7 +8144,9 @@
       <ns0:c r="P74" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q74"/>
+      <ns0:c s="1" r="Q74" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="75" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A75" s="6" t="n">
@@ -7866,7 +8158,9 @@
       <ns0:c r="C75" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D75" s="1"/>
+      <ns0:c r="D75" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
       <ns0:c r="E75" s="1" t="n">
         <ns0:v>486.8</ns0:v>
       </ns0:c>
@@ -7903,7 +8197,9 @@
       <ns0:c r="P75" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q75"/>
+      <ns0:c s="1" r="Q75" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="76" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A76" s="6" t="n">
@@ -7915,7 +8211,9 @@
       <ns0:c r="C76" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D76" s="1"/>
+      <ns0:c r="D76" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
       <ns0:c r="E76" s="1" t="n">
         <ns0:v>469.54</ns0:v>
       </ns0:c>
@@ -7952,7 +8250,9 @@
       <ns0:c r="P76" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q76"/>
+      <ns0:c s="1" r="Q76" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="77" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A77" s="6" t="n">
@@ -7964,7 +8264,9 @@
       <ns0:c r="C77" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D77" s="1"/>
+      <ns0:c r="D77" s="1" t="n">
+        <ns0:v>420</ns0:v>
+      </ns0:c>
       <ns0:c r="E77" s="1" t="n">
         <ns0:v>432.58</ns0:v>
       </ns0:c>
@@ -8001,7 +8303,9 @@
       <ns0:c r="P77" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q77"/>
+      <ns0:c s="1" r="Q77" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="78" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A78" s="6" t="n">
@@ -8013,7 +8317,9 @@
       <ns0:c r="C78" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D78" s="1"/>
+      <ns0:c r="D78" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E78" s="1" t="n">
         <ns0:v>432.58</ns0:v>
       </ns0:c>
@@ -8050,7 +8356,9 @@
       <ns0:c r="P78" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q78"/>
+      <ns0:c s="1" r="Q78" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="79" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A79" s="6" t="n">
@@ -8062,7 +8370,9 @@
       <ns0:c r="C79" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D79" s="1"/>
+      <ns0:c r="D79" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E79" s="1" t="n">
         <ns0:v>435.26</ns0:v>
       </ns0:c>
@@ -8099,7 +8409,9 @@
       <ns0:c r="P79" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q79"/>
+      <ns0:c s="1" r="Q79" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="80" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A80" s="6" t="n">
@@ -8111,7 +8423,9 @@
       <ns0:c r="C80" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D80" s="1"/>
+      <ns0:c r="D80" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E80" s="1" t="n">
         <ns0:v>282.82</ns0:v>
       </ns0:c>
@@ -8148,7 +8462,9 @@
       <ns0:c r="P80" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q80"/>
+      <ns0:c s="1" r="Q80" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="81" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A81" s="6" t="n">
@@ -8160,7 +8476,9 @@
       <ns0:c r="C81" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D81" s="1"/>
+      <ns0:c r="D81" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E81" s="1" t="n">
         <ns0:v>394.48</ns0:v>
       </ns0:c>
@@ -8197,7 +8515,9 @@
       <ns0:c r="P81" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q81"/>
+      <ns0:c s="1" r="Q81" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="82" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A82" s="6" t="n">
@@ -8209,7 +8529,9 @@
       <ns0:c r="C82" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D82" s="1"/>
+      <ns0:c r="D82" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E82" s="1" t="n">
         <ns0:v>471.57</ns0:v>
       </ns0:c>
@@ -8246,7 +8568,9 @@
       <ns0:c r="P82" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q82"/>
+      <ns0:c s="1" r="Q82" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="83" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A83" s="6" t="n">
@@ -8258,7 +8582,9 @@
       <ns0:c r="C83" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D83" s="1"/>
+      <ns0:c r="D83" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E83" s="1" t="n">
         <ns0:v>465.52</ns0:v>
       </ns0:c>
@@ -8295,7 +8621,9 @@
       <ns0:c r="P83" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q83"/>
+      <ns0:c s="1" r="Q83" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="84" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A84" s="6" t="n">
@@ -8307,7 +8635,9 @@
       <ns0:c r="C84" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D84" s="1"/>
+      <ns0:c r="D84" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E84" s="1" t="n">
         <ns0:v>426.3</ns0:v>
       </ns0:c>
@@ -8344,7 +8674,9 @@
       <ns0:c r="P84" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q84"/>
+      <ns0:c s="1" r="Q84" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="85" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A85" s="6" t="n">
@@ -8356,7 +8688,9 @@
       <ns0:c r="C85" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D85" s="1"/>
+      <ns0:c r="D85" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E85" s="1" t="n">
         <ns0:v>480</ns0:v>
       </ns0:c>
@@ -8393,7 +8727,9 @@
       <ns0:c r="P85" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q85"/>
+      <ns0:c s="1" r="Q85" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="86" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A86" s="6" t="n">
@@ -8405,7 +8741,9 @@
       <ns0:c r="C86" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D86" s="1"/>
+      <ns0:c r="D86" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E86" s="1" t="n">
         <ns0:v>480</ns0:v>
       </ns0:c>
@@ -8442,7 +8780,9 @@
       <ns0:c r="P86" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q86"/>
+      <ns0:c s="1" r="Q86" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="87" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A87" s="6" t="n">
@@ -8454,7 +8794,9 @@
       <ns0:c r="C87" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D87" s="1"/>
+      <ns0:c r="D87" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E87" s="1" t="n">
         <ns0:v>469</ns0:v>
       </ns0:c>
@@ -8491,7 +8833,9 @@
       <ns0:c r="P87" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q87"/>
+      <ns0:c s="1" r="Q87" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="88" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A88" s="6" t="n">
@@ -8503,7 +8847,9 @@
       <ns0:c r="C88" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D88" s="1"/>
+      <ns0:c r="D88" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E88" s="1" t="n">
         <ns0:v>426.3</ns0:v>
       </ns0:c>
@@ -8540,7 +8886,9 @@
       <ns0:c r="P88" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q88"/>
+      <ns0:c s="1" r="Q88" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="89" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A89" s="6" t="n">
@@ -8552,7 +8900,9 @@
       <ns0:c r="C89" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D89" s="1"/>
+      <ns0:c r="D89" s="1" t="n">
+        <ns0:v>390.61</ns0:v>
+      </ns0:c>
       <ns0:c r="E89" s="1" t="n">
         <ns0:v>404.2</ns0:v>
       </ns0:c>
@@ -8589,7 +8939,9 @@
       <ns0:c r="P89" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q89"/>
+      <ns0:c s="1" r="Q89" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="90" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A90" s="6" t="n">
@@ -8601,7 +8953,9 @@
       <ns0:c r="C90" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D90" s="1"/>
+      <ns0:c r="D90" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E90" s="1" t="n">
         <ns0:v>422.45</ns0:v>
       </ns0:c>
@@ -8638,7 +8992,9 @@
       <ns0:c r="P90" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q90"/>
+      <ns0:c s="1" r="Q90" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="91" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A91" s="6" t="n">
@@ -8650,7 +9006,9 @@
       <ns0:c r="C91" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D91" s="1"/>
+      <ns0:c r="D91" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E91" s="1" t="n">
         <ns0:v>402.54</ns0:v>
       </ns0:c>
@@ -8687,7 +9045,9 @@
       <ns0:c r="P91" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q91"/>
+      <ns0:c s="1" r="Q91" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="92" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A92" s="6" t="n">
@@ -8699,7 +9059,9 @@
       <ns0:c r="C92" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D92" s="1"/>
+      <ns0:c r="D92" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E92" s="1" t="n">
         <ns0:v>334.67</ns0:v>
       </ns0:c>
@@ -8736,7 +9098,9 @@
       <ns0:c r="P92" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q92"/>
+      <ns0:c s="1" r="Q92" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="93" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A93" s="6" t="n">
@@ -8748,7 +9112,9 @@
       <ns0:c r="C93" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D93" s="1"/>
+      <ns0:c r="D93" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E93" s="1" t="n">
         <ns0:v>417.22</ns0:v>
       </ns0:c>
@@ -8785,7 +9151,9 @@
       <ns0:c r="P93" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q93"/>
+      <ns0:c s="1" r="Q93" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="94" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A94" s="6" t="n">
@@ -8797,7 +9165,9 @@
       <ns0:c r="C94" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D94" s="1"/>
+      <ns0:c r="D94" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E94" s="1" t="n">
         <ns0:v>469.54</ns0:v>
       </ns0:c>
@@ -8834,7 +9204,9 @@
       <ns0:c r="P94" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q94"/>
+      <ns0:c s="1" r="Q94" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="95" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A95" s="6" t="n">
@@ -8846,7 +9218,9 @@
       <ns0:c r="C95" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D95" s="1"/>
+      <ns0:c r="D95" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E95" s="1" t="n">
         <ns0:v>423.26</ns0:v>
       </ns0:c>
@@ -8883,7 +9257,9 @@
       <ns0:c r="P95" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q95"/>
+      <ns0:c s="1" r="Q95" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="96" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A96" s="6" t="n">
@@ -8895,7 +9271,9 @@
       <ns0:c r="C96" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D96" s="1"/>
+      <ns0:c r="D96" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E96" s="1" t="n">
         <ns0:v>404.2</ns0:v>
       </ns0:c>
@@ -8932,7 +9310,9 @@
       <ns0:c r="P96" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q96"/>
+      <ns0:c s="1" r="Q96" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="97" s="1" customFormat="1" spans="1:16">
       <ns0:c r="A97" s="6" t="n">
@@ -8946,7 +9326,9 @@
       <ns0:c r="C97" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D97" s="1"/>
+      <ns0:c r="D97" s="1" t="n">
+        <ns0:v>330</ns0:v>
+      </ns0:c>
       <ns0:c r="E97" s="1" t="n">
         <ns0:v>402.8</ns0:v>
       </ns0:c>
@@ -8983,7 +9365,9 @@
       <ns0:c r="P97" s="1" t="n">
         <ns0:v>62</ns0:v>
       </ns0:c>
-      <ns0:c s="1" r="Q97"/>
+      <ns0:c s="1" r="Q97" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
     </ns0:row>
   </ns0:sheetData>
   <conditionalFormatting sqref="A1:B1">
